--- a/Result/profitability/3150.xlsx
+++ b/Result/profitability/3150.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM43"/>
+  <dimension ref="A1:AM44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.22</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0175</v>
+        <v>-0.055</v>
       </c>
       <c r="N2" t="n">
-        <v>46.62375</v>
+        <v>46.2675</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.3</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.02375</v>
+        <v>-0.01375000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>46.7325</v>
+        <v>46.5</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.5</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0825</v>
+        <v>-0.09875</v>
       </c>
       <c r="N4" t="n">
-        <v>46.43375</v>
+        <v>46.09125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0.24</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.07500000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="N5" t="n">
-        <v>45.55375</v>
+        <v>45.95625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -5891,6 +5891,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>3150</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>89</v>
+      </c>
+      <c r="D44" t="n">
+        <v>48</v>
+      </c>
+      <c r="E44" t="n">
+        <v>40</v>
+      </c>
+      <c r="F44" t="n">
+        <v>45.33</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-0.23%</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.01625</v>
+      </c>
+      <c r="N44" t="n">
+        <v>45.18</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="X44" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.109999999999999</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0.025101763907734</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>-1.714285714285714</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>3.219999999999999</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.07646639753027773</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK44" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
